--- a/templates/Shablon_300_zhurnal.xlsx
+++ b/templates/Shablon_300_zhurnal.xlsx
@@ -557,7 +557,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A22"/>
+  <dimension ref="A1:A29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -671,36 +671,81 @@
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr"/>
+    </row>
     <row r="18">
-      <c r="A18" s="4" t="inlineStr">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Як користуватися аркушем «Довідники»</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>• Кожна колонка аркуша — один список (Статус, Виконавці, Осередки, Бригади…). Саме з них беруться варіанти у випадаючих меню журналу.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>• Додати варіант: впишіть його в першу порожню клітинку під списком — він одразу з’явиться в меню (місце є до 300-го рядка).</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>• Не перейменовуйте й не видаляйте значення, які вже обрані в журналі: старі рядки не оновляться й стануть «помилковими». Краще додайте новий варіант, а старий залиште.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>• Новий виконавець, осередок чи бригада з’явилися — додайте їх у «Довідники» й повідомте адміністратора реєстру, щоб додати й там.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>• Аркуш «Довідники» варто захистити (Дані → Захистити аркуші), щоб змінювати його міг лише відповідальний.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
         <is>
           <t>Кольори заголовків — блоки колонок:</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
         <is>
           <t>Облік і робота ГО</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="6" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
         <is>
           <t>Стан / документи</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="7" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="7" t="inlineStr">
         <is>
           <t>Поранений (основна картка)</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="8" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="8" t="inlineStr">
         <is>
           <t>Інші родичі (2 і 3)</t>
         </is>
@@ -14370,17 +14415,17 @@
   <autoFilter ref="A1:AG1"/>
   <dataValidations count="21">
     <dataValidation sqref="B2:B1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Невірне значення" error="Оберіть значення зі списку" type="list">
-      <formula1>=Довідники!$A$2:$A$6</formula1>
+      <formula1>=Довідники!$A$2:$A$300</formula1>
     </dataValidation>
     <dataValidation sqref="C2:C1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Невірна дата" error="Введіть дату у форматі ДД.ММ.РРРР" type="date" operator="between">
       <formula1>DATE(1900,1,1)</formula1>
       <formula2>DATE(2100,12,31)</formula2>
     </dataValidation>
     <dataValidation sqref="D2:D1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Невірне значення" error="Оберіть значення зі списку" type="list">
-      <formula1>=Довідники!$B$2:$B$19</formula1>
+      <formula1>=Довідники!$B$2:$B$300</formula1>
     </dataValidation>
     <dataValidation sqref="E2:E1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Невірне значення" error="Оберіть значення зі списку" type="list">
-      <formula1>=Довідники!$C$2:$C$6</formula1>
+      <formula1>=Довідники!$C$2:$C$300</formula1>
     </dataValidation>
     <dataValidation sqref="F2:F1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Невірна дата" error="Введіть дату у форматі ДД.ММ.РРРР" type="date" operator="between">
       <formula1>DATE(1900,1,1)</formula1>
@@ -14391,7 +14436,7 @@
       <formula2>DATE(2100,12,31)</formula2>
     </dataValidation>
     <dataValidation sqref="K2:K1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Невірне значення" error="Оберіть значення зі списку" type="list">
-      <formula1>=Довідники!$D$2:$D$19</formula1>
+      <formula1>=Довідники!$D$2:$D$300</formula1>
     </dataValidation>
     <dataValidation sqref="L2:L1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Невірний телефон" error="Один номер: 10 цифр без пробілів (0501234567) або закордонний з + (+48512345678)" type="custom">
       <formula1>OR(AND(LEN(L2)=10,LEFT(L2,1)="0",ISNUMBER(VALUE(L2))),AND(LEFT(L2,1)="+",LEN(L2)&gt;=11,LEN(L2)&lt;=16))</formula1>
@@ -14400,38 +14445,38 @@
       <formula1>OR(AND(LEN(M2)=10,LEFT(M2,1)="0",ISNUMBER(VALUE(M2))),AND(LEFT(M2,1)="+",LEN(M2)&gt;=11,LEN(M2)&lt;=16))</formula1>
     </dataValidation>
     <dataValidation sqref="N2:N1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Невірне значення" error="Оберіть значення зі списку" type="list">
-      <formula1>=Довідники!$E$2:$E$24</formula1>
+      <formula1>=Довідники!$E$2:$E$300</formula1>
     </dataValidation>
     <dataValidation sqref="O2:O1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Невірне значення" error="Оберіть значення зі списку" type="list">
-      <formula1>=Довідники!$F$2:$F$25</formula1>
+      <formula1>=Довідники!$F$2:$F$300</formula1>
     </dataValidation>
     <dataValidation sqref="P2:P1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Невірна дата" error="Введіть дату у форматі ДД.ММ.РРРР" type="date" operator="between">
       <formula1>DATE(1900,1,1)</formula1>
       <formula2>DATE(2100,12,31)</formula2>
     </dataValidation>
     <dataValidation sqref="Q2:Q1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Невірне значення" error="Оберіть значення зі списку" type="list">
-      <formula1>=Довідники!$G$2:$G$4</formula1>
+      <formula1>=Довідники!$G$2:$G$300</formula1>
     </dataValidation>
     <dataValidation sqref="R2:R1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Невірне значення" error="Оберіть значення зі списку" type="list">
-      <formula1>=Довідники!$H$2:$H$4</formula1>
+      <formula1>=Довідники!$H$2:$H$300</formula1>
     </dataValidation>
     <dataValidation sqref="S2:S1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Невірне значення" error="Оберіть значення зі списку" type="list">
-      <formula1>=Довідники!$H$2:$H$4</formula1>
+      <formula1>=Довідники!$H$2:$H$300</formula1>
     </dataValidation>
     <dataValidation sqref="W2:W1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Невірне значення" error="Оберіть значення зі списку" type="list">
-      <formula1>=Довідники!$I$2:$I$16</formula1>
+      <formula1>=Довідники!$I$2:$I$300</formula1>
     </dataValidation>
     <dataValidation sqref="Y2:Y1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Невірний телефон" error="Один номер: 10 цифр без пробілів (0501234567) або закордонний з + (+48512345678)" type="custom">
       <formula1>OR(AND(LEN(Y2)=10,LEFT(Y2,1)="0",ISNUMBER(VALUE(Y2))),AND(LEFT(Y2,1)="+",LEN(Y2)&gt;=11,LEN(Y2)&lt;=16))</formula1>
     </dataValidation>
     <dataValidation sqref="Z2:Z1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Невірне значення" error="Оберіть значення зі списку" type="list">
-      <formula1>=Довідники!$I$2:$I$16</formula1>
+      <formula1>=Довідники!$I$2:$I$300</formula1>
     </dataValidation>
     <dataValidation sqref="AB2:AB1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Невірний телефон" error="Один номер: 10 цифр без пробілів (0501234567) або закордонний з + (+48512345678)" type="custom">
       <formula1>OR(AND(LEN(AB2)=10,LEFT(AB2,1)="0",ISNUMBER(VALUE(AB2))),AND(LEFT(AB2,1)="+",LEN(AB2)&gt;=11,LEN(AB2)&lt;=16))</formula1>
     </dataValidation>
     <dataValidation sqref="AC2:AC1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Невірне значення" error="Оберіть значення зі списку" type="list">
-      <formula1>=Довідники!$I$2:$I$16</formula1>
+      <formula1>=Довідники!$I$2:$I$300</formula1>
     </dataValidation>
     <dataValidation sqref="AE2:AE1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Невірний телефон" error="Один номер: 10 цифр без пробілів (0501234567) або закордонний з + (+48512345678)" type="custom">
       <formula1>OR(AND(LEN(AE2)=10,LEFT(AE2,1)="0",ISNUMBER(VALUE(AE2))),AND(LEFT(AE2,1)="+",LEN(AE2)&gt;=11,LEN(AE2)&lt;=16))</formula1>

--- a/templates/Shablon_300_zhurnal.xlsx
+++ b/templates/Shablon_300_zhurnal.xlsx
@@ -240,31 +240,6 @@
     </indexedColors>
   </colors>
 </styleSheet>
-</file>
-
-<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>Реєстр</author>
-  </authors>
-  <commentList>
-    <comment ref="A1" authorId="0" shapeId="0">
-      <text>
-        <t>Унікальний номер рядка: 300-0001, 300-0002… Не змінювати.</t>
-      </text>
-    </comment>
-    <comment ref="E1" authorId="0" shapeId="0">
-      <text>
-        <t>Якщо «Помер» — заповніть «Дата смерті». Система звірить із журналом 200.</t>
-      </text>
-    </comment>
-    <comment ref="A2" authorId="0" shapeId="0">
-      <text>
-        <t>Рядок-ПРИКЛАД: покажіть колегам, як заповнювати, і видаліть його перед роботою.</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -14483,7 +14458,6 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 

--- a/templates/Shablon_300_zhurnal.xlsx
+++ b/templates/Shablon_300_zhurnal.xlsx
@@ -14390,17 +14390,17 @@
   <autoFilter ref="A1:AG1"/>
   <dataValidations count="21">
     <dataValidation sqref="B2:B1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Невірне значення" error="Оберіть значення зі списку" type="list">
-      <formula1>=Довідники!$A$2:$A$300</formula1>
+      <formula1>'Довідники'!$A$2:$A$300</formula1>
     </dataValidation>
     <dataValidation sqref="C2:C1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Невірна дата" error="Введіть дату у форматі ДД.ММ.РРРР" type="date" operator="between">
       <formula1>DATE(1900,1,1)</formula1>
       <formula2>DATE(2100,12,31)</formula2>
     </dataValidation>
     <dataValidation sqref="D2:D1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Невірне значення" error="Оберіть значення зі списку" type="list">
-      <formula1>=Довідники!$B$2:$B$300</formula1>
+      <formula1>'Довідники'!$B$2:$B$300</formula1>
     </dataValidation>
     <dataValidation sqref="E2:E1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Невірне значення" error="Оберіть значення зі списку" type="list">
-      <formula1>=Довідники!$C$2:$C$300</formula1>
+      <formula1>'Довідники'!$C$2:$C$300</formula1>
     </dataValidation>
     <dataValidation sqref="F2:F1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Невірна дата" error="Введіть дату у форматі ДД.ММ.РРРР" type="date" operator="between">
       <formula1>DATE(1900,1,1)</formula1>
@@ -14411,7 +14411,7 @@
       <formula2>DATE(2100,12,31)</formula2>
     </dataValidation>
     <dataValidation sqref="K2:K1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Невірне значення" error="Оберіть значення зі списку" type="list">
-      <formula1>=Довідники!$D$2:$D$300</formula1>
+      <formula1>'Довідники'!$D$2:$D$300</formula1>
     </dataValidation>
     <dataValidation sqref="L2:L1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Невірний телефон" error="Один номер: 10 цифр без пробілів (0501234567) або закордонний з + (+48512345678)" type="custom">
       <formula1>OR(AND(LEN(L2)=10,LEFT(L2,1)="0",ISNUMBER(VALUE(L2))),AND(LEFT(L2,1)="+",LEN(L2)&gt;=11,LEN(L2)&lt;=16))</formula1>
@@ -14420,38 +14420,38 @@
       <formula1>OR(AND(LEN(M2)=10,LEFT(M2,1)="0",ISNUMBER(VALUE(M2))),AND(LEFT(M2,1)="+",LEN(M2)&gt;=11,LEN(M2)&lt;=16))</formula1>
     </dataValidation>
     <dataValidation sqref="N2:N1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Невірне значення" error="Оберіть значення зі списку" type="list">
-      <formula1>=Довідники!$E$2:$E$300</formula1>
+      <formula1>'Довідники'!$E$2:$E$300</formula1>
     </dataValidation>
     <dataValidation sqref="O2:O1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Невірне значення" error="Оберіть значення зі списку" type="list">
-      <formula1>=Довідники!$F$2:$F$300</formula1>
+      <formula1>'Довідники'!$F$2:$F$300</formula1>
     </dataValidation>
     <dataValidation sqref="P2:P1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Невірна дата" error="Введіть дату у форматі ДД.ММ.РРРР" type="date" operator="between">
       <formula1>DATE(1900,1,1)</formula1>
       <formula2>DATE(2100,12,31)</formula2>
     </dataValidation>
     <dataValidation sqref="Q2:Q1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Невірне значення" error="Оберіть значення зі списку" type="list">
-      <formula1>=Довідники!$G$2:$G$300</formula1>
+      <formula1>'Довідники'!$G$2:$G$300</formula1>
     </dataValidation>
     <dataValidation sqref="R2:R1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Невірне значення" error="Оберіть значення зі списку" type="list">
-      <formula1>=Довідники!$H$2:$H$300</formula1>
+      <formula1>'Довідники'!$H$2:$H$300</formula1>
     </dataValidation>
     <dataValidation sqref="S2:S1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Невірне значення" error="Оберіть значення зі списку" type="list">
-      <formula1>=Довідники!$H$2:$H$300</formula1>
+      <formula1>'Довідники'!$H$2:$H$300</formula1>
     </dataValidation>
     <dataValidation sqref="W2:W1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Невірне значення" error="Оберіть значення зі списку" type="list">
-      <formula1>=Довідники!$I$2:$I$300</formula1>
+      <formula1>'Довідники'!$I$2:$I$300</formula1>
     </dataValidation>
     <dataValidation sqref="Y2:Y1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Невірний телефон" error="Один номер: 10 цифр без пробілів (0501234567) або закордонний з + (+48512345678)" type="custom">
       <formula1>OR(AND(LEN(Y2)=10,LEFT(Y2,1)="0",ISNUMBER(VALUE(Y2))),AND(LEFT(Y2,1)="+",LEN(Y2)&gt;=11,LEN(Y2)&lt;=16))</formula1>
     </dataValidation>
     <dataValidation sqref="Z2:Z1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Невірне значення" error="Оберіть значення зі списку" type="list">
-      <formula1>=Довідники!$I$2:$I$300</formula1>
+      <formula1>'Довідники'!$I$2:$I$300</formula1>
     </dataValidation>
     <dataValidation sqref="AB2:AB1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Невірний телефон" error="Один номер: 10 цифр без пробілів (0501234567) або закордонний з + (+48512345678)" type="custom">
       <formula1>OR(AND(LEN(AB2)=10,LEFT(AB2,1)="0",ISNUMBER(VALUE(AB2))),AND(LEFT(AB2,1)="+",LEN(AB2)&gt;=11,LEN(AB2)&lt;=16))</formula1>
     </dataValidation>
     <dataValidation sqref="AC2:AC1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Невірне значення" error="Оберіть значення зі списку" type="list">
-      <formula1>=Довідники!$I$2:$I$300</formula1>
+      <formula1>'Довідники'!$I$2:$I$300</formula1>
     </dataValidation>
     <dataValidation sqref="AE2:AE1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Невірний телефон" error="Один номер: 10 цифр без пробілів (0501234567) або закордонний з + (+48512345678)" type="custom">
       <formula1>OR(AND(LEN(AE2)=10,LEFT(AE2,1)="0",ISNUMBER(VALUE(AE2))),AND(LEFT(AE2,1)="+",LEN(AE2)&gt;=11,LEN(AE2)&lt;=16))</formula1>
